--- a/Assets/GameResource/Excel/物品表.xlsx
+++ b/Assets/GameResource/Excel/物品表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD47DDE-38E9-4877-BD54-90BE9B6719D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97339D4-EBA3-49EA-981C-5AC50AD7EFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>木头</t>
   </si>
   <si>
-    <t>村落常用的低级材料</t>
-  </si>
-  <si>
     <t>石头</t>
   </si>
   <si>
@@ -98,16 +95,10 @@
     <t>水银</t>
   </si>
   <si>
-    <t>村落常用的中级材料</t>
-  </si>
-  <si>
     <t>硫磺</t>
   </si>
   <si>
     <t>水晶</t>
-  </si>
-  <si>
-    <t>村落常用的高级材料</t>
   </si>
   <si>
     <t>宝石</t>
@@ -125,6 +116,17 @@
   <si>
     <t>道具标签
 多个用逗号隔开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小镇建造所需的基础材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常见的基础材料</t>
+  </si>
+  <si>
+    <t>常见的基础材料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,6 +145,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -499,7 +502,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -519,7 +522,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
@@ -561,8 +564,8 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>16</v>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -573,7 +576,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -581,8 +584,8 @@
       <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" t="s">
-        <v>16</v>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -593,7 +596,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -601,8 +604,8 @@
       <c r="D7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
-        <v>16</v>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -613,7 +616,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -621,8 +624,8 @@
       <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
-        <v>16</v>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -633,7 +636,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -641,8 +644,8 @@
       <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" t="s">
-        <v>21</v>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -653,7 +656,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
@@ -661,8 +664,8 @@
       <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
+      <c r="E10" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -673,7 +676,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -681,8 +684,8 @@
       <c r="D11" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
-        <v>24</v>
+      <c r="E11" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -693,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -701,8 +704,8 @@
       <c r="D12" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
-        <v>24</v>
+      <c r="E12" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F12">
         <v>9</v>
@@ -713,7 +716,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -722,7 +725,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F13">
         <v>10</v>
